--- a/apps/api/data/excel_templates/industries.xlsx
+++ b/apps/api/data/excel_templates/industries.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valentindaveau/Bildix/Website/Bildyx/apps/api/data/excel/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/valentindaveau/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{492E3E5B-311F-9941-A7C6-3DC5E299B87F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{347F0B3D-3544-4141-9569-64FFA4E4D835}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="29400" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="20740" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="industries" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="147">
   <si>
     <t>name</t>
   </si>
@@ -41,13 +41,437 @@
   </si>
   <si>
     <t>score</t>
+  </si>
+  <si>
+    <t>Agriculture and Forestry</t>
+  </si>
+  <si>
+    <t>Mining</t>
+  </si>
+  <si>
+    <t>Automotive</t>
+  </si>
+  <si>
+    <t>Chemical Industry</t>
+  </si>
+  <si>
+    <t>Construction</t>
+  </si>
+  <si>
+    <t>Durable Consumer Goods</t>
+  </si>
+  <si>
+    <t>Electronics</t>
+  </si>
+  <si>
+    <t>Energy</t>
+  </si>
+  <si>
+    <t>Fast-Moving Consumer Goods (FMCG)</t>
+  </si>
+  <si>
+    <t>Food Industry</t>
+  </si>
+  <si>
+    <t>Heavy Manufacturing</t>
+  </si>
+  <si>
+    <t>Industrial Goods</t>
+  </si>
+  <si>
+    <t>Medical Devices</t>
+  </si>
+  <si>
+    <t>Office and Communication Equipment</t>
+  </si>
+  <si>
+    <t>Pharmaceutical</t>
+  </si>
+  <si>
+    <t>Utilities</t>
+  </si>
+  <si>
+    <t>Advertising &amp; Marketing</t>
+  </si>
+  <si>
+    <t>Banking</t>
+  </si>
+  <si>
+    <t>Business Services</t>
+  </si>
+  <si>
+    <t>Entertainment and Broadcasting</t>
+  </si>
+  <si>
+    <t>Financial Services</t>
+  </si>
+  <si>
+    <t>Hospitality</t>
+  </si>
+  <si>
+    <t>Insurance</t>
+  </si>
+  <si>
+    <t>Legal Services</t>
+  </si>
+  <si>
+    <t>Management Consulting</t>
+  </si>
+  <si>
+    <t>Personal Services</t>
+  </si>
+  <si>
+    <t>Publishing</t>
+  </si>
+  <si>
+    <t>Real Estate</t>
+  </si>
+  <si>
+    <t>Recruitment</t>
+  </si>
+  <si>
+    <t>Retail</t>
+  </si>
+  <si>
+    <t>Transport</t>
+  </si>
+  <si>
+    <t>Computer Hardware</t>
+  </si>
+  <si>
+    <t>Computer Software</t>
+  </si>
+  <si>
+    <t>Enterprise Software</t>
+  </si>
+  <si>
+    <t>Gaming Industry</t>
+  </si>
+  <si>
+    <t>Industry Specific Software</t>
+  </si>
+  <si>
+    <t>IT Services</t>
+  </si>
+  <si>
+    <t>Mobile Applications</t>
+  </si>
+  <si>
+    <t>Online Services</t>
+  </si>
+  <si>
+    <t>PC Consumer Software</t>
+  </si>
+  <si>
+    <t>Robotics</t>
+  </si>
+  <si>
+    <t>Semiconductor</t>
+  </si>
+  <si>
+    <t>Telecommunications</t>
+  </si>
+  <si>
+    <t>Education</t>
+  </si>
+  <si>
+    <t>Army</t>
+  </si>
+  <si>
+    <t>Government</t>
+  </si>
+  <si>
+    <t>Delivers public administration, policy development, regulation, and public services. Includes local, regional, and national government agencies. Supports economic development, public safety, healthcare, education, and infrastructure.</t>
+  </si>
+  <si>
+    <t>Protects national security through military operations, defense planning, and peacekeeping activities. Employs personnel in combat, engineering, intelligence, logistics, healthcare, and administration. Focuses on readiness, discipline, and national defense.</t>
+  </si>
+  <si>
+    <t>Provides teaching, learning, training, and academic research services. Includes schools, universities, vocational institutions, and educational technology providers. Develops knowledge, skills, and workforce capabilities.</t>
+  </si>
+  <si>
+    <t>Provides voice, data, internet, and wireless communication services. Builds and operates communication networks and infrastructure. Supports businesses, governments, and consumers worldwide.</t>
+  </si>
+  <si>
+    <t>Designs and manufactures integrated circuits, microprocessors, memory chips, and electronic components. Forms the foundation of modern computing and communications. Requires advanced fabrication technologies and significant research investment.</t>
+  </si>
+  <si>
+    <t>Designs and builds robotic systems for manufacturing, healthcare, logistics, and service applications. Combines mechanical engineering, electronics, and artificial intelligence. Improves automation, productivity, and precision.</t>
+  </si>
+  <si>
+    <t>Develops desktop software for productivity, creativity, security, and entertainment. Serves individual users and small businesses. Emphasizes usability, compatibility, and regular feature updates.</t>
+  </si>
+  <si>
+    <t>Delivers internet-based services such as e-commerce, cloud platforms, streaming, social media, and digital marketplaces. Operates through web and mobile technologies. Business models often rely on subscriptions, advertising, or transactions.</t>
+  </si>
+  <si>
+    <t>Designs and develops software for smartphones, tablets, and mobile devices. Covers consumer apps, enterprise solutions, and mobile commerce. Focuses on usability, performance, and continuous updates.</t>
+  </si>
+  <si>
+    <t>Provides technology consulting, systems integration, cloud services, cybersecurity, and technical support. Helps organizations implement and manage IT infrastructure. Enables digital transformation and operational efficiency.</t>
+  </si>
+  <si>
+    <t>Develops software tailored to specialized industries such as healthcare, finance, manufacturing, or education. Addresses unique regulatory and operational requirements. Enables organizations to improve productivity and compliance.</t>
+  </si>
+  <si>
+    <t>Develops, publishes, and distributes video games across consoles, PCs, and mobile devices. Combines software development, storytelling, design, and online services. Revenue comes from game sales, subscriptions, and in-game purchases.</t>
+  </si>
+  <si>
+    <t>Creates software solutions for business operations such as ERP, CRM, finance, and HR systems. Helps organizations improve efficiency and decision-making. Typically serves medium and large enterprises.</t>
+  </si>
+  <si>
+    <t>Develops software applications and operating systems for personal and business use. Covers design, coding, testing, and maintenance. Drives digital transformation across industries.</t>
+  </si>
+  <si>
+    <t>Designs and manufactures computers, servers, storage devices, and related hardware. Focuses on performance, reliability, and innovation. Supports consumer, enterprise, and industrial computing.</t>
+  </si>
+  <si>
+    <t>Moves people and goods by road, rail, air, and sea. Includes logistics, freight, shipping, and public transportation. Plays a vital role in global trade and economic activity.</t>
+  </si>
+  <si>
+    <t>Sells products directly to consumers through physical stores and online platforms. Manages merchandising, customer service, and inventory. Success depends on consumer demand and efficient supply chains.</t>
+  </si>
+  <si>
+    <t>Helps organizations attract, assess, and hire employees. Provides staffing, executive search, and workforce solutions. Supports employers across industries and job levels.</t>
+  </si>
+  <si>
+    <t>Develops, buys, sells, leases, and manages residential and commercial properties. Includes property investment, construction, and facility management. Supports housing, business, and infrastructure needs.</t>
+  </si>
+  <si>
+    <t>Produces books, journals, newspapers, magazines, and digital publications. Manages editorial, production, and content distribution processes. Increasingly emphasizes digital platforms and online content.</t>
+  </si>
+  <si>
+    <t>Delivers services directly to consumers, including beauty, wellness, fitness, and personal care. Focuses on customer relationships and service quality. Demand is driven by lifestyle and consumer preferences.</t>
+  </si>
+  <si>
+    <t>Advises organizations on strategy, operations, technology, and organizational improvement. Helps clients solve business challenges and improve performance. Consultants work across many industries and functions.</t>
+  </si>
+  <si>
+    <t>Provides legal advice, representation, compliance, and dispute resolution. Serves businesses, governments, and individuals. Requires expertise in laws, regulations, and legal procedures.</t>
+  </si>
+  <si>
+    <t>Protects individuals and organizations against financial losses through insurance products. Covers life, health, property, and commercial risks. Relies on underwriting, actuarial analysis, and claims management.</t>
+  </si>
+  <si>
+    <t>Provides accommodation, food service, tourism, and event management. Focuses on customer experience and service quality. Includes hotels, restaurants, resorts, and travel businesses.</t>
+  </si>
+  <si>
+    <t>Offers investment, asset management, brokerage, lending, and financial advisory services. Helps individuals and organizations manage capital and financial risks. Relies on regulatory compliance and financial expertise.</t>
+  </si>
+  <si>
+    <t>Produces and distributes television, radio, film, music, and digital media content. Combines creativity with media technology and distribution platforms. Generates revenue through advertising, subscriptions, and licensing.</t>
+  </si>
+  <si>
+    <t>Delivers professional support such as outsourcing, administration, customer service, and facility management. Helps organizations improve efficiency and reduce costs. Serves businesses across multiple industries.</t>
+  </si>
+  <si>
+    <t>Provides financial services including deposits, loans, payments, and wealth management. Supports individuals, businesses, and governments. Operates under strict financial regulations and risk management standards.</t>
+  </si>
+  <si>
+    <t>Creates campaigns that promote brands, products, and services. Uses market research, creative content, digital platforms, and analytics. Helps organizations attract and retain customers.</t>
+  </si>
+  <si>
+    <t>Provides essential public services including electricity, water, gas, and wastewater management. Operates critical infrastructure with high reliability requirements. Often functions under government regulation.</t>
+  </si>
+  <si>
+    <t>Discovers, develops, manufactures, and markets medicines and vaccines. Invests heavily in research, clinical trials, and regulatory approval. Improves healthcare outcomes through innovative therapies.</t>
+  </si>
+  <si>
+    <t>Produces office machines, printers, networking equipment, and communication hardware. Supports workplace productivity and business communications. Continuously evolves with advances in digital technology.</t>
+  </si>
+  <si>
+    <t>Designs and manufactures equipment used for diagnosis, monitoring, and treatment. Products range from surgical instruments to advanced imaging systems. Strict quality standards and regulatory compliance are essential.</t>
+  </si>
+  <si>
+    <t>Manufactures machinery, tools, industrial equipment, and production materials for businesses. Focuses on efficiency, reliability, and automation. Supplies manufacturing, construction, and infrastructure industries.</t>
+  </si>
+  <si>
+    <t>Produces large-scale industrial equipment, machinery, ships, and heavy infrastructure components. Requires advanced engineering and significant capital investment. Supports construction, transportation, and energy sectors.</t>
+  </si>
+  <si>
+    <t>Processes, manufactures, packages, and distributes food and beverages. Ensures product quality, food safety, and regulatory compliance. Serves consumers, retailers, and food service businesses worldwide.</t>
+  </si>
+  <si>
+    <t>Produces and markets everyday products such as food, beverages, toiletries, and household items. Operates with high sales volumes and rapid inventory turnover. Success depends on branding, distribution, and supply chains.</t>
+  </si>
+  <si>
+    <t>Produces and distributes electricity, oil, natural gas, and renewable energy. Invests in power generation, energy storage, and sustainability initiatives. Plays a critical role in economic development.</t>
+  </si>
+  <si>
+    <t>Develops and manufactures electronic devices, components, and systems. Includes consumer electronics, industrial equipment, and embedded technologies. Innovation and rapid product development are key drivers.</t>
+  </si>
+  <si>
+    <t>Manufactures long-lasting consumer products such as appliances, furniture, and household equipment. Focuses on product quality, innovation, and customer satisfaction. Products are typically used for several years.</t>
+  </si>
+  <si>
+    <t>Plans, builds, and maintains residential, commercial, and infrastructure projects. Includes architecture, engineering, project management, and skilled trades. Drives urban development and economic growth.</t>
+  </si>
+  <si>
+    <t>Produces industrial chemicals, plastics, fertilizers, coatings, and specialty materials. Supports numerous sectors including agriculture, healthcare, and manufacturing. Emphasizes innovation, safety, and environmental compliance.</t>
+  </si>
+  <si>
+    <t>Designs, manufactures, and sells cars, trucks, motorcycles, and vehicle components. Covers electric vehicles, autonomous driving, and mobility technologies. Employs engineers, technicians, and manufacturing specialists.</t>
+  </si>
+  <si>
+    <t>Manufactures paper, cardboard, packaging, and pulp products from wood and recycled fibers. Focuses on sustainable production and recycling. Serves publishing, packaging, and consumer goods markets.</t>
+  </si>
+  <si>
+    <t>Pulp and Paper Industry</t>
+  </si>
+  <si>
+    <t>Extracts minerals, metals, coal, and other natural resources from the earth. Uses exploration, drilling, and processing technologies. Supplies essential materials for manufacturing, energy, and construction.</t>
+  </si>
+  <si>
+    <t>Produces crops, livestock, timber, and other natural resources. Includes farming, forestry management, and agricultural technology. Supports global food supply, raw materials, and environmental sustainability.</t>
+  </si>
+  <si>
+    <t>IND-000001</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>IND-000002</t>
+  </si>
+  <si>
+    <t>IND-000003</t>
+  </si>
+  <si>
+    <t>IND-000004</t>
+  </si>
+  <si>
+    <t>IND-000005</t>
+  </si>
+  <si>
+    <t>IND-000006</t>
+  </si>
+  <si>
+    <t>IND-000007</t>
+  </si>
+  <si>
+    <t>IND-000008</t>
+  </si>
+  <si>
+    <t>IND-000009</t>
+  </si>
+  <si>
+    <t>IND-000010</t>
+  </si>
+  <si>
+    <t>IND-000011</t>
+  </si>
+  <si>
+    <t>IND-000012</t>
+  </si>
+  <si>
+    <t>IND-000013</t>
+  </si>
+  <si>
+    <t>IND-000014</t>
+  </si>
+  <si>
+    <t>IND-000015</t>
+  </si>
+  <si>
+    <t>IND-000016</t>
+  </si>
+  <si>
+    <t>IND-000017</t>
+  </si>
+  <si>
+    <t>IND-000018</t>
+  </si>
+  <si>
+    <t>IND-000019</t>
+  </si>
+  <si>
+    <t>IND-000020</t>
+  </si>
+  <si>
+    <t>IND-000021</t>
+  </si>
+  <si>
+    <t>IND-000022</t>
+  </si>
+  <si>
+    <t>IND-000023</t>
+  </si>
+  <si>
+    <t>IND-000024</t>
+  </si>
+  <si>
+    <t>IND-000025</t>
+  </si>
+  <si>
+    <t>IND-000026</t>
+  </si>
+  <si>
+    <t>IND-000027</t>
+  </si>
+  <si>
+    <t>IND-000028</t>
+  </si>
+  <si>
+    <t>IND-000029</t>
+  </si>
+  <si>
+    <t>IND-000030</t>
+  </si>
+  <si>
+    <t>IND-000031</t>
+  </si>
+  <si>
+    <t>IND-000032</t>
+  </si>
+  <si>
+    <t>IND-000033</t>
+  </si>
+  <si>
+    <t>IND-000034</t>
+  </si>
+  <si>
+    <t>IND-000035</t>
+  </si>
+  <si>
+    <t>IND-000036</t>
+  </si>
+  <si>
+    <t>IND-000037</t>
+  </si>
+  <si>
+    <t>IND-000038</t>
+  </si>
+  <si>
+    <t>IND-000039</t>
+  </si>
+  <si>
+    <t>IND-000040</t>
+  </si>
+  <si>
+    <t>IND-000041</t>
+  </si>
+  <si>
+    <t>IND-000042</t>
+  </si>
+  <si>
+    <t>IND-000043</t>
+  </si>
+  <si>
+    <t>IND-000044</t>
+  </si>
+  <si>
+    <t>IND-000045</t>
+  </si>
+  <si>
+    <t>IND-000046</t>
+  </si>
+  <si>
+    <t>IND-000047</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -58,21 +482,24 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="6"/>
       <name val="Calibri"/>
-      <family val="2"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -89,8 +516,10 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -393,34 +822,552 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:F48"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="6" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4" t="s">
+        <v>102</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>103</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>104</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+      <c r="B9" t="s">
+        <v>107</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" t="s">
+        <v>109</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>110</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" t="s">
+        <v>16</v>
+      </c>
+      <c r="B13" t="s">
+        <v>111</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" t="s">
+        <v>17</v>
+      </c>
+      <c r="B14" t="s">
+        <v>112</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" t="s">
+        <v>113</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" t="s">
+        <v>114</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>20</v>
+      </c>
+      <c r="B17" t="s">
+        <v>115</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" t="s">
+        <v>116</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>22</v>
+      </c>
+      <c r="B19" t="s">
+        <v>117</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>23</v>
+      </c>
+      <c r="B20" t="s">
+        <v>118</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>25</v>
+      </c>
+      <c r="B22" t="s">
+        <v>120</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" t="s">
+        <v>26</v>
+      </c>
+      <c r="B23" t="s">
+        <v>121</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>27</v>
+      </c>
+      <c r="B24" t="s">
+        <v>122</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B25" t="s">
+        <v>123</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>29</v>
+      </c>
+      <c r="B26" t="s">
+        <v>124</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B27" t="s">
+        <v>125</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>31</v>
+      </c>
+      <c r="B28" t="s">
+        <v>126</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>32</v>
+      </c>
+      <c r="B29" t="s">
+        <v>127</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" t="s">
+        <v>128</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
+      <c r="A31" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" t="s">
+        <v>129</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" t="s">
+        <v>130</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" t="s">
+        <v>36</v>
+      </c>
+      <c r="B33" t="s">
+        <v>131</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
+      <c r="A34" t="s">
+        <v>37</v>
+      </c>
+      <c r="B34" t="s">
+        <v>132</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
+      <c r="A35" t="s">
+        <v>38</v>
+      </c>
+      <c r="B35" t="s">
+        <v>133</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
+      <c r="A36" t="s">
+        <v>39</v>
+      </c>
+      <c r="B36" t="s">
+        <v>134</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
+      <c r="A37" t="s">
+        <v>40</v>
+      </c>
+      <c r="B37" t="s">
+        <v>135</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3">
+      <c r="A38" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" t="s">
+        <v>136</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
+      <c r="A39" t="s">
+        <v>42</v>
+      </c>
+      <c r="B39" t="s">
+        <v>137</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
+      <c r="A40" t="s">
+        <v>43</v>
+      </c>
+      <c r="B40" t="s">
+        <v>138</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
+      <c r="A41" t="s">
+        <v>44</v>
+      </c>
+      <c r="B41" t="s">
+        <v>139</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
+      <c r="A42" t="s">
+        <v>45</v>
+      </c>
+      <c r="B42" t="s">
+        <v>140</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
+      <c r="A43" t="s">
+        <v>46</v>
+      </c>
+      <c r="B43" t="s">
+        <v>141</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
+      <c r="A44" t="s">
+        <v>47</v>
+      </c>
+      <c r="B44" t="s">
+        <v>142</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
+      <c r="A45" t="s">
+        <v>48</v>
+      </c>
+      <c r="B45" t="s">
+        <v>143</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
+      <c r="A46" t="s">
+        <v>49</v>
+      </c>
+      <c r="B46" t="s">
+        <v>144</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3">
+      <c r="A47" t="s">
+        <v>50</v>
+      </c>
+      <c r="B47" t="s">
+        <v>145</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
+      <c r="A48" t="s">
+        <v>51</v>
+      </c>
+      <c r="B48" t="s">
+        <v>146</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <phoneticPr fontId="2"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/apps/api/data/excel_templates/industries.xlsx
+++ b/apps/api/data/excel_templates/industries.xlsx
@@ -1424,7 +1424,7 @@
       <c r="F48" s="3" t="n"/>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <autoFilter ref="A1:F1"/>
   <dataValidations count="1">
     <dataValidation sqref="F2:F1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid number" error="Please enter a whole number." type="whole" operator="between">

--- a/apps/api/data/excel_templates/industries.xlsx
+++ b/apps/api/data/excel_templates/industries.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="1" min="1" max="1"/>
@@ -440,6 +440,7 @@
     <col width="18" customWidth="1" style="1" min="4" max="4"/>
     <col width="18" customWidth="1" style="1" min="5" max="5"/>
     <col width="18" customWidth="1" style="2" min="6" max="6"/>
+    <col width="22" customWidth="1" style="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -471,6 +472,11 @@
       <c r="F1" s="4" t="inlineStr">
         <is>
           <t>score</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>related_industries</t>
         </is>
       </c>
     </row>

--- a/apps/api/data/excel_templates/industries.xlsx
+++ b/apps/api/data/excel_templates/industries.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection lockStructure="1"/>
+  <workbookProtection workbookPassword="DB2D" lockStructure="1"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
@@ -481,7 +481,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1" password="DB2D"/>
   <autoFilter ref="A1:F1"/>
   <dataValidations count="1">
     <dataValidation sqref="F2:F1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid number" error="Please enter a whole number." type="whole" operator="between">

--- a/apps/api/data/excel_templates/industries.xlsx
+++ b/apps/api/data/excel_templates/industries.xlsx
@@ -56,7 +56,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
@@ -66,6 +66,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -431,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" style="1" min="1" max="1"/>
@@ -480,6 +483,993 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>Agriculture and Forestry</t>
+        </is>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>IND-000001</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Produces crops, livestock, timber, and other natural resources. Includes farming, forestry management, and agricultural technology. Supports global food supply, raw materials, and environmental sustainability.</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="5" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>Mining</t>
+        </is>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>IND-000002</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>Extracts minerals, metals, coal, and other natural resources from the earth. Uses exploration, drilling, and processing technologies. Supplies essential materials for manufacturing, energy, and construction.</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Pulp and Paper Industry</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>IND-000003</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Manufactures paper, cardboard, packaging, and pulp products from wood and recycled fibers. Focuses on sustainable production and recycling. Serves publishing, packaging, and consumer goods markets.</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Automotive</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>IND-000004</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Designs, manufactures, and sells cars, trucks, motorcycles, and vehicle components. Covers electric vehicles, autonomous driving, and mobility technologies. Employs engineers, technicians, and manufacturing specialists.</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>Chemical Industry</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>IND-000005</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Produces industrial chemicals, plastics, fertilizers, coatings, and specialty materials. Supports numerous sectors including agriculture, healthcare, and manufacturing. Emphasizes innovation, safety, and environmental compliance.</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Construction</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>IND-000006</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Plans, builds, and maintains residential, commercial, and infrastructure projects. Includes architecture, engineering, project management, and skilled trades. Drives urban development and economic growth.</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Durable Consumer Goods</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>IND-000007</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Manufactures long-lasting consumer products such as appliances, furniture, and household equipment. Focuses on product quality, innovation, and customer satisfaction. Products are typically used for several years.</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Electronics</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>IND-000008</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Develops and manufactures electronic devices, components, and systems. Includes consumer electronics, industrial equipment, and embedded technologies. Innovation and rapid product development are key drivers.</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>IND-000009</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Produces and distributes electricity, oil, natural gas, and renewable energy. Invests in power generation, energy storage, and sustainability initiatives. Plays a critical role in economic development.</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Fast-Moving Consumer Goods (FMCG)</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>IND-000010</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Produces and markets everyday products such as food, beverages, toiletries, and household items. Operates with high sales volumes and rapid inventory turnover. Success depends on branding, distribution, and supply chains.</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Food Industry</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>IND-000011</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Processes, manufactures, packages, and distributes food and beverages. Ensures product quality, food safety, and regulatory compliance. Serves consumers, retailers, and food service businesses worldwide.</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Heavy Manufacturing</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>IND-000012</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Produces large-scale industrial equipment, machinery, ships, and heavy infrastructure components. Requires advanced engineering and significant capital investment. Supports construction, transportation, and energy sectors.</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Industrial Goods</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>IND-000013</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Manufactures machinery, tools, industrial equipment, and production materials for businesses. Focuses on efficiency, reliability, and automation. Supplies manufacturing, construction, and infrastructure industries.</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Medical Devices</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>IND-000014</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>Designs and manufactures equipment used for diagnosis, monitoring, and treatment. Products range from surgical instruments to advanced imaging systems. Strict quality standards and regulatory compliance are essential.</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>Office and Communication Equipment</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>IND-000015</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Produces office machines, printers, networking equipment, and communication hardware. Supports workplace productivity and business communications. Continuously evolves with advances in digital technology.</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>Pharmaceutical</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>IND-000016</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Discovers, develops, manufactures, and markets medicines and vaccines. Invests heavily in research, clinical trials, and regulatory approval. Improves healthcare outcomes through innovative therapies.</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>IND-000017</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Provides essential public services including electricity, water, gas, and wastewater management. Operates critical infrastructure with high reliability requirements. Often functions under government regulation.</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Advertising &amp; Marketing</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>IND-000018</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Creates campaigns that promote brands, products, and services. Uses market research, creative content, digital platforms, and analytics. Helps organizations attract and retain customers.</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Banking</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>IND-000019</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Provides financial services including deposits, loans, payments, and wealth management. Supports individuals, businesses, and governments. Operates under strict financial regulations and risk management standards.</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Business Services</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>IND-000020</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Delivers professional support such as outsourcing, administration, customer service, and facility management. Helps organizations improve efficiency and reduce costs. Serves businesses across multiple industries.</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Entertainment and Broadcasting</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>IND-000021</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Produces and distributes television, radio, film, music, and digital media content. Combines creativity with media technology and distribution platforms. Generates revenue through advertising, subscriptions, and licensing.</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>IND-000022</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Offers investment, asset management, brokerage, lending, and financial advisory services. Helps individuals and organizations manage capital and financial risks. Relies on regulatory compliance and financial expertise.</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Hospitality</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>IND-000023</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Provides accommodation, food service, tourism, and event management. Focuses on customer experience and service quality. Includes hotels, restaurants, resorts, and travel businesses.</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Insurance</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>IND-000024</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Protects individuals and organizations against financial losses through insurance products. Covers life, health, property, and commercial risks. Relies on underwriting, actuarial analysis, and claims management.</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Legal Services</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>IND-000025</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Provides legal advice, representation, compliance, and dispute resolution. Serves businesses, governments, and individuals. Requires expertise in laws, regulations, and legal procedures.</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Management Consulting</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>IND-000026</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Advises organizations on strategy, operations, technology, and organizational improvement. Helps clients solve business challenges and improve performance. Consultants work across many industries and functions.</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Personal Services</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>IND-000027</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Delivers services directly to consumers, including beauty, wellness, fitness, and personal care. Focuses on customer relationships and service quality. Demand is driven by lifestyle and consumer preferences.</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Publishing</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>IND-000028</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Produces books, journals, newspapers, magazines, and digital publications. Manages editorial, production, and content distribution processes. Increasingly emphasizes digital platforms and online content.</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>Real Estate</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>IND-000029</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Develops, buys, sells, leases, and manages residential and commercial properties. Includes property investment, construction, and facility management. Supports housing, business, and infrastructure needs.</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>Recruitment</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>IND-000030</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Helps organizations attract, assess, and hire employees. Provides staffing, executive search, and workforce solutions. Supports employers across industries and job levels.</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>IND-000031</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Sells products directly to consumers through physical stores and online platforms. Manages merchandising, customer service, and inventory. Success depends on consumer demand and efficient supply chains.</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>IND-000032</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Moves people and goods by road, rail, air, and sea. Includes logistics, freight, shipping, and public transportation. Plays a vital role in global trade and economic activity.</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>Computer Hardware</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>IND-000033</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Designs and manufactures computers, servers, storage devices, and related hardware. Focuses on performance, reliability, and innovation. Supports consumer, enterprise, and industrial computing.</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>Computer Software</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>IND-000034</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Develops software applications and operating systems for personal and business use. Covers design, coding, testing, and maintenance. Drives digital transformation across industries.</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Enterprise Software</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>IND-000035</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Creates software solutions for business operations such as ERP, CRM, finance, and HR systems. Helps organizations improve efficiency and decision-making. Typically serves medium and large enterprises.</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>Gaming Industry</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>IND-000036</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Develops, publishes, and distributes video games across consoles, PCs, and mobile devices. Combines software development, storytelling, design, and online services. Revenue comes from game sales, subscriptions, and in-game purchases.</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>Industry Specific Software</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>IND-000037</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Develops software tailored to specialized industries such as healthcare, finance, manufacturing, or education. Addresses unique regulatory and operational requirements. Enables organizations to improve productivity and compliance.</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="5" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>IT Services</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>IND-000038</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Provides technology consulting, systems integration, cloud services, cybersecurity, and technical support. Helps organizations implement and manage IT infrastructure. Enables digital transformation and operational efficiency.</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Mobile Applications</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>IND-000039</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Designs and develops software for smartphones, tablets, and mobile devices. Covers consumer apps, enterprise solutions, and mobile commerce. Focuses on usability, performance, and continuous updates.</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="5" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>Online Services</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>IND-000040</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Delivers internet-based services such as e-commerce, cloud platforms, streaming, social media, and digital marketplaces. Operates through web and mobile technologies. Business models often rely on subscriptions, advertising, or transactions.</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="5" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>PC Consumer Software</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>IND-000041</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>Develops desktop software for productivity, creativity, security, and entertainment. Serves individual users and small businesses. Emphasizes usability, compatibility, and regular feature updates.</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="n"/>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="n"/>
+      <c r="G42" s="5" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Robotics</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>IND-000042</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Designs and builds robotic systems for manufacturing, healthcare, logistics, and service applications. Combines mechanical engineering, electronics, and artificial intelligence. Improves automation, productivity, and precision.</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="5" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Semiconductor</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>IND-000043</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Designs and manufactures integrated circuits, microprocessors, memory chips, and electronic components. Forms the foundation of modern computing and communications. Requires advanced fabrication technologies and significant research investment.</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="n"/>
+      <c r="G44" s="5" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Telecommunications</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>IND-000044</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Provides voice, data, internet, and wireless communication services. Builds and operates communication networks and infrastructure. Supports businesses, governments, and consumers worldwide.</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="n"/>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="n"/>
+      <c r="G45" s="5" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Education</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>IND-000045</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Provides teaching, learning, training, and academic research services. Includes schools, universities, vocational institutions, and educational technology providers. Develops knowledge, skills, and workforce capabilities.</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="n"/>
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="n"/>
+      <c r="G46" s="5" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>Army</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>IND-000046</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Protects national security through military operations, defense planning, and peacekeeping activities. Employs personnel in combat, engineering, intelligence, logistics, healthcare, and administration. Focuses on readiness, discipline, and national defense.</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="n"/>
+      <c r="G47" s="5" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Government</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>IND-000047</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>Delivers public administration, policy development, regulation, and public services. Includes local, regional, and national government agencies. Supports economic development, public safety, healthcare, education, and infrastructure.</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="n"/>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="n"/>
+      <c r="G48" s="5" t="n"/>
+    </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <autoFilter ref="A1:F1"/>

--- a/apps/api/data/excel_templates/industries.xlsx
+++ b/apps/api/data/excel_templates/industries.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="industries" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'industries'!$A$1:$F$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'industries'!$A$1:$G$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -56,7 +56,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
@@ -66,9 +66,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -484,995 +481,807 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Agriculture and Forestry</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>IND-000001</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Produces crops, livestock, timber, and other natural resources. Includes farming, forestry management, and agricultural technology. Supports global food supply, raw materials, and environmental sustainability.</t>
         </is>
       </c>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="5" t="n"/>
-      <c r="F2" s="5" t="n"/>
-      <c r="G2" s="5" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>IND-000002</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Extracts minerals, metals, coal, and other natural resources from the earth. Uses exploration, drilling, and processing technologies. Supplies essential materials for manufacturing, energy, and construction.</t>
         </is>
       </c>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Pulp and Paper Industry</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>IND-000003</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Manufactures paper, cardboard, packaging, and pulp products from wood and recycled fibers. Focuses on sustainable production and recycling. Serves publishing, packaging, and consumer goods markets.</t>
         </is>
       </c>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Automotive</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>IND-000004</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Designs, manufactures, and sells cars, trucks, motorcycles, and vehicle components. Covers electric vehicles, autonomous driving, and mobility technologies. Employs engineers, technicians, and manufacturing specialists.</t>
         </is>
       </c>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Chemical Industry</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>IND-000005</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Produces industrial chemicals, plastics, fertilizers, coatings, and specialty materials. Supports numerous sectors including agriculture, healthcare, and manufacturing. Emphasizes innovation, safety, and environmental compliance.</t>
         </is>
       </c>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Construction</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>IND-000006</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Plans, builds, and maintains residential, commercial, and infrastructure projects. Includes architecture, engineering, project management, and skilled trades. Drives urban development and economic growth.</t>
         </is>
       </c>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Durable Consumer Goods</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>IND-000007</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Manufactures long-lasting consumer products such as appliances, furniture, and household equipment. Focuses on product quality, innovation, and customer satisfaction. Products are typically used for several years.</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>IND-000008</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Develops and manufactures electronic devices, components, and systems. Includes consumer electronics, industrial equipment, and embedded technologies. Innovation and rapid product development are key drivers.</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>IND-000009</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Produces and distributes electricity, oil, natural gas, and renewable energy. Invests in power generation, energy storage, and sustainability initiatives. Plays a critical role in economic development.</t>
         </is>
       </c>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Fast-Moving Consumer Goods (FMCG)</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>IND-000010</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Produces and markets everyday products such as food, beverages, toiletries, and household items. Operates with high sales volumes and rapid inventory turnover. Success depends on branding, distribution, and supply chains.</t>
         </is>
       </c>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Food Industry</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>IND-000011</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Processes, manufactures, packages, and distributes food and beverages. Ensures product quality, food safety, and regulatory compliance. Serves consumers, retailers, and food service businesses worldwide.</t>
         </is>
       </c>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Heavy Manufacturing</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>IND-000012</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Produces large-scale industrial equipment, machinery, ships, and heavy infrastructure components. Requires advanced engineering and significant capital investment. Supports construction, transportation, and energy sectors.</t>
         </is>
       </c>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Industrial Goods</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>IND-000013</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Manufactures machinery, tools, industrial equipment, and production materials for businesses. Focuses on efficiency, reliability, and automation. Supplies manufacturing, construction, and infrastructure industries.</t>
         </is>
       </c>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>IND-000014</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Designs and manufactures equipment used for diagnosis, monitoring, and treatment. Products range from surgical instruments to advanced imaging systems. Strict quality standards and regulatory compliance are essential.</t>
         </is>
       </c>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Office and Communication Equipment</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>IND-000015</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Produces office machines, printers, networking equipment, and communication hardware. Supports workplace productivity and business communications. Continuously evolves with advances in digital technology.</t>
         </is>
       </c>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Pharmaceutical</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>IND-000016</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Discovers, develops, manufactures, and markets medicines and vaccines. Invests heavily in research, clinical trials, and regulatory approval. Improves healthcare outcomes through innovative therapies.</t>
         </is>
       </c>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Utilities</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>IND-000017</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Provides essential public services including electricity, water, gas, and wastewater management. Operates critical infrastructure with high reliability requirements. Often functions under government regulation.</t>
         </is>
       </c>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Advertising &amp; Marketing</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>IND-000018</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Creates campaigns that promote brands, products, and services. Uses market research, creative content, digital platforms, and analytics. Helps organizations attract and retain customers.</t>
         </is>
       </c>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Banking</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>IND-000019</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Provides financial services including deposits, loans, payments, and wealth management. Supports individuals, businesses, and governments. Operates under strict financial regulations and risk management standards.</t>
         </is>
       </c>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Business Services</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>IND-000020</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Delivers professional support such as outsourcing, administration, customer service, and facility management. Helps organizations improve efficiency and reduce costs. Serves businesses across multiple industries.</t>
         </is>
       </c>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Entertainment and Broadcasting</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>IND-000021</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Produces and distributes television, radio, film, music, and digital media content. Combines creativity with media technology and distribution platforms. Generates revenue through advertising, subscriptions, and licensing.</t>
         </is>
       </c>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>IND-000022</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Offers investment, asset management, brokerage, lending, and financial advisory services. Helps individuals and organizations manage capital and financial risks. Relies on regulatory compliance and financial expertise.</t>
         </is>
       </c>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Hospitality</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>IND-000023</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Provides accommodation, food service, tourism, and event management. Focuses on customer experience and service quality. Includes hotels, restaurants, resorts, and travel businesses.</t>
         </is>
       </c>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>IND-000024</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Protects individuals and organizations against financial losses through insurance products. Covers life, health, property, and commercial risks. Relies on underwriting, actuarial analysis, and claims management.</t>
         </is>
       </c>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Legal Services</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>IND-000025</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Provides legal advice, representation, compliance, and dispute resolution. Serves businesses, governments, and individuals. Requires expertise in laws, regulations, and legal procedures.</t>
         </is>
       </c>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Management Consulting</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>IND-000026</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Advises organizations on strategy, operations, technology, and organizational improvement. Helps clients solve business challenges and improve performance. Consultants work across many industries and functions.</t>
         </is>
       </c>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Personal Services</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>IND-000027</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Delivers services directly to consumers, including beauty, wellness, fitness, and personal care. Focuses on customer relationships and service quality. Demand is driven by lifestyle and consumer preferences.</t>
         </is>
       </c>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Publishing</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>IND-000028</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Produces books, journals, newspapers, magazines, and digital publications. Manages editorial, production, and content distribution processes. Increasingly emphasizes digital platforms and online content.</t>
         </is>
       </c>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>IND-000029</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Develops, buys, sells, leases, and manages residential and commercial properties. Includes property investment, construction, and facility management. Supports housing, business, and infrastructure needs.</t>
         </is>
       </c>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="5" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Recruitment</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>IND-000030</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Helps organizations attract, assess, and hire employees. Provides staffing, executive search, and workforce solutions. Supports employers across industries and job levels.</t>
         </is>
       </c>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Retail</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>IND-000031</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Sells products directly to consumers through physical stores and online platforms. Manages merchandising, customer service, and inventory. Success depends on consumer demand and efficient supply chains.</t>
         </is>
       </c>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
-      <c r="G32" s="5" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Transport</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>IND-000032</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Moves people and goods by road, rail, air, and sea. Includes logistics, freight, shipping, and public transportation. Plays a vital role in global trade and economic activity.</t>
         </is>
       </c>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Computer Hardware</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>IND-000033</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Designs and manufactures computers, servers, storage devices, and related hardware. Focuses on performance, reliability, and innovation. Supports consumer, enterprise, and industrial computing.</t>
         </is>
       </c>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Computer Software</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>IND-000034</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Develops software applications and operating systems for personal and business use. Covers design, coding, testing, and maintenance. Drives digital transformation across industries.</t>
         </is>
       </c>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="n"/>
-      <c r="G35" s="5" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Enterprise Software</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>IND-000035</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Creates software solutions for business operations such as ERP, CRM, finance, and HR systems. Helps organizations improve efficiency and decision-making. Typically serves medium and large enterprises.</t>
         </is>
       </c>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5" t="n"/>
-      <c r="G36" s="5" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Gaming Industry</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>IND-000036</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Develops, publishes, and distributes video games across consoles, PCs, and mobile devices. Combines software development, storytelling, design, and online services. Revenue comes from game sales, subscriptions, and in-game purchases.</t>
         </is>
       </c>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="5" t="n"/>
-      <c r="F37" s="5" t="n"/>
-      <c r="G37" s="5" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Industry Specific Software</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>IND-000037</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Develops software tailored to specialized industries such as healthcare, finance, manufacturing, or education. Addresses unique regulatory and operational requirements. Enables organizations to improve productivity and compliance.</t>
         </is>
       </c>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5" t="n"/>
-      <c r="G38" s="5" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>IT Services</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>IND-000038</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Provides technology consulting, systems integration, cloud services, cybersecurity, and technical support. Helps organizations implement and manage IT infrastructure. Enables digital transformation and operational efficiency.</t>
         </is>
       </c>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5" t="n"/>
-      <c r="G39" s="5" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Mobile Applications</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>IND-000039</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Designs and develops software for smartphones, tablets, and mobile devices. Covers consumer apps, enterprise solutions, and mobile commerce. Focuses on usability, performance, and continuous updates.</t>
         </is>
       </c>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="n"/>
-      <c r="G40" s="5" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Online Services</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>IND-000040</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Delivers internet-based services such as e-commerce, cloud platforms, streaming, social media, and digital marketplaces. Operates through web and mobile technologies. Business models often rely on subscriptions, advertising, or transactions.</t>
         </is>
       </c>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="n"/>
-      <c r="G41" s="5" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>PC Consumer Software</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>IND-000041</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Develops desktop software for productivity, creativity, security, and entertainment. Serves individual users and small businesses. Emphasizes usability, compatibility, and regular feature updates.</t>
         </is>
       </c>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="n"/>
-      <c r="G42" s="5" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>Robotics</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>IND-000042</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Designs and builds robotic systems for manufacturing, healthcare, logistics, and service applications. Combines mechanical engineering, electronics, and artificial intelligence. Improves automation, productivity, and precision.</t>
         </is>
       </c>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5" t="n"/>
-      <c r="G43" s="5" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>Semiconductor</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>IND-000043</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Designs and manufactures integrated circuits, microprocessors, memory chips, and electronic components. Forms the foundation of modern computing and communications. Requires advanced fabrication technologies and significant research investment.</t>
         </is>
       </c>
-      <c r="D44" s="5" t="n"/>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="5" t="n"/>
-      <c r="G44" s="5" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>Telecommunications</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>IND-000044</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Provides voice, data, internet, and wireless communication services. Builds and operates communication networks and infrastructure. Supports businesses, governments, and consumers worldwide.</t>
         </is>
       </c>
-      <c r="D45" s="5" t="n"/>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="n"/>
-      <c r="G45" s="5" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>IND-000045</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Provides teaching, learning, training, and academic research services. Includes schools, universities, vocational institutions, and educational technology providers. Develops knowledge, skills, and workforce capabilities.</t>
         </is>
       </c>
-      <c r="D46" s="5" t="n"/>
-      <c r="E46" s="5" t="n"/>
-      <c r="F46" s="5" t="n"/>
-      <c r="G46" s="5" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>Army</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>IND-000046</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Protects national security through military operations, defense planning, and peacekeeping activities. Employs personnel in combat, engineering, intelligence, logistics, healthcare, and administration. Focuses on readiness, discipline, and national defense.</t>
         </is>
       </c>
-      <c r="D47" s="5" t="n"/>
-      <c r="E47" s="5" t="n"/>
-      <c r="F47" s="5" t="n"/>
-      <c r="G47" s="5" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>Government</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>IND-000047</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Delivers public administration, policy development, regulation, and public services. Includes local, regional, and national government agencies. Supports economic development, public safety, healthcare, education, and infrastructure.</t>
         </is>
       </c>
-      <c r="D48" s="5" t="n"/>
-      <c r="E48" s="5" t="n"/>
-      <c r="F48" s="5" t="n"/>
-      <c r="G48" s="5" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1" password="DB2D"/>
-  <autoFilter ref="A1:F1"/>
+  <autoFilter ref="A1:G1"/>
   <dataValidations count="1">
     <dataValidation sqref="F2:F1048576" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Invalid number" error="Please enter a whole number." type="whole" operator="between">
       <formula1>-2147483648</formula1>

--- a/apps/api/data/excel_templates/industries.xlsx
+++ b/apps/api/data/excel_templates/industries.xlsx
@@ -56,7 +56,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
@@ -66,6 +66,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -481,803 +484,991 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>Agriculture and Forestry</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B2" s="5" t="inlineStr">
         <is>
           <t>IND-000001</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C2" s="5" t="inlineStr">
         <is>
           <t>Produces crops, livestock, timber, and other natural resources. Includes farming, forestry management, and agricultural technology. Supports global food supply, raw materials, and environmental sustainability.</t>
         </is>
       </c>
+      <c r="D2" s="5" t="n"/>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="5" t="n"/>
+      <c r="G2" s="5" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>IND-000002</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Extracts minerals, metals, coal, and other natural resources from the earth. Uses exploration, drilling, and processing technologies. Supplies essential materials for manufacturing, energy, and construction.</t>
         </is>
       </c>
+      <c r="D3" s="5" t="n"/>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="n"/>
+      <c r="G3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Pulp and Paper Industry</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>IND-000003</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Manufactures paper, cardboard, packaging, and pulp products from wood and recycled fibers. Focuses on sustainable production and recycling. Serves publishing, packaging, and consumer goods markets.</t>
         </is>
       </c>
+      <c r="D4" s="5" t="n"/>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Automotive</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>IND-000004</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Designs, manufactures, and sells cars, trucks, motorcycles, and vehicle components. Covers electric vehicles, autonomous driving, and mobility technologies. Employs engineers, technicians, and manufacturing specialists.</t>
         </is>
       </c>
+      <c r="D5" s="5" t="n"/>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="n"/>
+      <c r="G5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Chemical Industry</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>IND-000005</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Produces industrial chemicals, plastics, fertilizers, coatings, and specialty materials. Supports numerous sectors including agriculture, healthcare, and manufacturing. Emphasizes innovation, safety, and environmental compliance.</t>
         </is>
       </c>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Construction</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>IND-000006</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Plans, builds, and maintains residential, commercial, and infrastructure projects. Includes architecture, engineering, project management, and skilled trades. Drives urban development and economic growth.</t>
         </is>
       </c>
+      <c r="D7" s="5" t="n"/>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
+      <c r="G7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Durable Consumer Goods</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>IND-000007</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Manufactures long-lasting consumer products such as appliances, furniture, and household equipment. Focuses on product quality, innovation, and customer satisfaction. Products are typically used for several years.</t>
         </is>
       </c>
+      <c r="D8" s="5" t="n"/>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
+      <c r="G8" s="5" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>IND-000008</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Develops and manufactures electronic devices, components, and systems. Includes consumer electronics, industrial equipment, and embedded technologies. Innovation and rapid product development are key drivers.</t>
         </is>
       </c>
+      <c r="D9" s="5" t="n"/>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="n"/>
+      <c r="G9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>IND-000009</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Produces and distributes electricity, oil, natural gas, and renewable energy. Invests in power generation, energy storage, and sustainability initiatives. Plays a critical role in economic development.</t>
         </is>
       </c>
+      <c r="D10" s="5" t="n"/>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="5" t="n"/>
+      <c r="G10" s="5" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Fast-Moving Consumer Goods (FMCG)</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>IND-000010</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Produces and markets everyday products such as food, beverages, toiletries, and household items. Operates with high sales volumes and rapid inventory turnover. Success depends on branding, distribution, and supply chains.</t>
         </is>
       </c>
+      <c r="D11" s="5" t="n"/>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="n"/>
+      <c r="G11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Food Industry</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>IND-000011</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Processes, manufactures, packages, and distributes food and beverages. Ensures product quality, food safety, and regulatory compliance. Serves consumers, retailers, and food service businesses worldwide.</t>
         </is>
       </c>
+      <c r="D12" s="5" t="n"/>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="5" t="n"/>
+      <c r="G12" s="5" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Heavy Manufacturing</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>IND-000012</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Produces large-scale industrial equipment, machinery, ships, and heavy infrastructure components. Requires advanced engineering and significant capital investment. Supports construction, transportation, and energy sectors.</t>
         </is>
       </c>
+      <c r="D13" s="5" t="n"/>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="5" t="n"/>
+      <c r="G13" s="5" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Industrial Goods</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>IND-000013</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>Manufactures machinery, tools, industrial equipment, and production materials for businesses. Focuses on efficiency, reliability, and automation. Supplies manufacturing, construction, and infrastructure industries.</t>
         </is>
       </c>
+      <c r="D14" s="5" t="n"/>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="5" t="n"/>
+      <c r="G14" s="5" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>IND-000014</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Designs and manufactures equipment used for diagnosis, monitoring, and treatment. Products range from surgical instruments to advanced imaging systems. Strict quality standards and regulatory compliance are essential.</t>
         </is>
       </c>
+      <c r="D15" s="5" t="n"/>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="5" t="n"/>
+      <c r="G15" s="5" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Office and Communication Equipment</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>IND-000015</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>Produces office machines, printers, networking equipment, and communication hardware. Supports workplace productivity and business communications. Continuously evolves with advances in digital technology.</t>
         </is>
       </c>
+      <c r="D16" s="5" t="n"/>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="5" t="n"/>
+      <c r="G16" s="5" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Pharmaceutical</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>IND-000016</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Discovers, develops, manufactures, and markets medicines and vaccines. Invests heavily in research, clinical trials, and regulatory approval. Improves healthcare outcomes through innovative therapies.</t>
         </is>
       </c>
+      <c r="D17" s="5" t="n"/>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="5" t="n"/>
+      <c r="G17" s="5" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Utilities</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>IND-000017</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Provides essential public services including electricity, water, gas, and wastewater management. Operates critical infrastructure with high reliability requirements. Often functions under government regulation.</t>
         </is>
       </c>
+      <c r="D18" s="5" t="n"/>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="5" t="n"/>
+      <c r="G18" s="5" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Advertising &amp; Marketing</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>IND-000018</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>Creates campaigns that promote brands, products, and services. Uses market research, creative content, digital platforms, and analytics. Helps organizations attract and retain customers.</t>
         </is>
       </c>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n"/>
+      <c r="G19" s="5" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Banking</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>IND-000019</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>Provides financial services including deposits, loans, payments, and wealth management. Supports individuals, businesses, and governments. Operates under strict financial regulations and risk management standards.</t>
         </is>
       </c>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
+      <c r="G20" s="5" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Business Services</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>IND-000020</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>Delivers professional support such as outsourcing, administration, customer service, and facility management. Helps organizations improve efficiency and reduce costs. Serves businesses across multiple industries.</t>
         </is>
       </c>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
+      <c r="G21" s="5" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Entertainment and Broadcasting</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>IND-000021</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>Produces and distributes television, radio, film, music, and digital media content. Combines creativity with media technology and distribution platforms. Generates revenue through advertising, subscriptions, and licensing.</t>
         </is>
       </c>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
+      <c r="G22" s="5" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>IND-000022</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>Offers investment, asset management, brokerage, lending, and financial advisory services. Helps individuals and organizations manage capital and financial risks. Relies on regulatory compliance and financial expertise.</t>
         </is>
       </c>
+      <c r="D23" s="5" t="n"/>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="n"/>
+      <c r="G23" s="5" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>Hospitality</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>IND-000023</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>Provides accommodation, food service, tourism, and event management. Focuses on customer experience and service quality. Includes hotels, restaurants, resorts, and travel businesses.</t>
         </is>
       </c>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
+      <c r="G24" s="5" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>IND-000024</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Protects individuals and organizations against financial losses through insurance products. Covers life, health, property, and commercial risks. Relies on underwriting, actuarial analysis, and claims management.</t>
         </is>
       </c>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
+      <c r="G25" s="5" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Legal Services</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>IND-000025</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>Provides legal advice, representation, compliance, and dispute resolution. Serves businesses, governments, and individuals. Requires expertise in laws, regulations, and legal procedures.</t>
         </is>
       </c>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
+      <c r="G26" s="5" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>Management Consulting</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>IND-000026</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>Advises organizations on strategy, operations, technology, and organizational improvement. Helps clients solve business challenges and improve performance. Consultants work across many industries and functions.</t>
         </is>
       </c>
+      <c r="D27" s="5" t="n"/>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="n"/>
+      <c r="G27" s="5" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>Personal Services</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>IND-000027</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>Delivers services directly to consumers, including beauty, wellness, fitness, and personal care. Focuses on customer relationships and service quality. Demand is driven by lifestyle and consumer preferences.</t>
         </is>
       </c>
+      <c r="D28" s="5" t="n"/>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="n"/>
+      <c r="G28" s="5" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>Publishing</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>IND-000028</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>Produces books, journals, newspapers, magazines, and digital publications. Manages editorial, production, and content distribution processes. Increasingly emphasizes digital platforms and online content.</t>
         </is>
       </c>
+      <c r="D29" s="5" t="n"/>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="n"/>
+      <c r="G29" s="5" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>IND-000029</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>Develops, buys, sells, leases, and manages residential and commercial properties. Includes property investment, construction, and facility management. Supports housing, business, and infrastructure needs.</t>
         </is>
       </c>
+      <c r="D30" s="5" t="n"/>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="n"/>
+      <c r="G30" s="5" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>Recruitment</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>IND-000030</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>Helps organizations attract, assess, and hire employees. Provides staffing, executive search, and workforce solutions. Supports employers across industries and job levels.</t>
         </is>
       </c>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+      <c r="G31" s="5" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>Retail</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>IND-000031</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>Sells products directly to consumers through physical stores and online platforms. Manages merchandising, customer service, and inventory. Success depends on consumer demand and efficient supply chains.</t>
         </is>
       </c>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+      <c r="G32" s="5" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>Transport</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>IND-000032</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>Moves people and goods by road, rail, air, and sea. Includes logistics, freight, shipping, and public transportation. Plays a vital role in global trade and economic activity.</t>
         </is>
       </c>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+      <c r="G33" s="5" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>Computer Hardware</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>IND-000033</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>Designs and manufactures computers, servers, storage devices, and related hardware. Focuses on performance, reliability, and innovation. Supports consumer, enterprise, and industrial computing.</t>
         </is>
       </c>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+      <c r="G34" s="5" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>Computer Software</t>
         </is>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>IND-000034</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>Develops software applications and operating systems for personal and business use. Covers design, coding, testing, and maintenance. Drives digital transformation across industries.</t>
         </is>
       </c>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="n"/>
+      <c r="G35" s="5" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>Enterprise Software</t>
         </is>
       </c>
-      <c r="B36" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>IND-000035</t>
         </is>
       </c>
-      <c r="C36" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>Creates software solutions for business operations such as ERP, CRM, finance, and HR systems. Helps organizations improve efficiency and decision-making. Typically serves medium and large enterprises.</t>
         </is>
       </c>
+      <c r="D36" s="5" t="n"/>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="5" t="n"/>
+      <c r="G36" s="5" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>Gaming Industry</t>
         </is>
       </c>
-      <c r="B37" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>IND-000036</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>Develops, publishes, and distributes video games across consoles, PCs, and mobile devices. Combines software development, storytelling, design, and online services. Revenue comes from game sales, subscriptions, and in-game purchases.</t>
         </is>
       </c>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n"/>
+      <c r="G37" s="5" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>Industry Specific Software</t>
         </is>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>IND-000037</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>Develops software tailored to specialized industries such as healthcare, finance, manufacturing, or education. Addresses unique regulatory and operational requirements. Enables organizations to improve productivity and compliance.</t>
         </is>
       </c>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+      <c r="G38" s="5" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>IT Services</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>IND-000038</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>Provides technology consulting, systems integration, cloud services, cybersecurity, and technical support. Helps organizations implement and manage IT infrastructure. Enables digital transformation and operational efficiency.</t>
         </is>
       </c>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+      <c r="G39" s="5" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>Mobile Applications</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>IND-000039</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>Designs and develops software for smartphones, tablets, and mobile devices. Covers consumer apps, enterprise solutions, and mobile commerce. Focuses on usability, performance, and continuous updates.</t>
         </is>
       </c>
+      <c r="D40" s="5" t="n"/>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="5" t="n"/>
+      <c r="G40" s="5" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>Online Services</t>
         </is>
       </c>
-      <c r="B41" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>IND-000040</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>Delivers internet-based services such as e-commerce, cloud platforms, streaming, social media, and digital marketplaces. Operates through web and mobile technologies. Business models often rely on subscriptions, advertising, or transactions.</t>
         </is>
       </c>
+      <c r="D41" s="5" t="n"/>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="5" t="n"/>
+      <c r="G41" s="5" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>PC Consumer Software</t>
         </is>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>IND-000041</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>Develops desktop software for productivity, creativity, security, and entertainment. Serves individual users and small businesses. Emphasizes usability, compatibility, and regular feature updates.</t>
         </is>
       </c>
+      <c r="D42" s="5" t="n"/>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="5" t="n"/>
+      <c r="G42" s="5" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>Robotics</t>
         </is>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>IND-000042</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>Designs and builds robotic systems for manufacturing, healthcare, logistics, and service applications. Combines mechanical engineering, electronics, and artificial intelligence. Improves automation, productivity, and precision.</t>
         </is>
       </c>
+      <c r="D43" s="5" t="n"/>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="5" t="n"/>
+      <c r="G43" s="5" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>Semiconductor</t>
         </is>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>IND-000043</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>Designs and manufactures integrated circuits, microprocessors, memory chips, and electronic components. Forms the foundation of modern computing and communications. Requires advanced fabrication technologies and significant research investment.</t>
         </is>
       </c>
+      <c r="D44" s="5" t="n"/>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="5" t="n"/>
+      <c r="G44" s="5" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>Telecommunications</t>
         </is>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>IND-000044</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>Provides voice, data, internet, and wireless communication services. Builds and operates communication networks and infrastructure. Supports businesses, governments, and consumers worldwide.</t>
         </is>
       </c>
+      <c r="D45" s="5" t="n"/>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="5" t="n"/>
+      <c r="G45" s="5" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" t="inlineStr">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>IND-000045</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>Provides teaching, learning, training, and academic research services. Includes schools, universities, vocational institutions, and educational technology providers. Develops knowledge, skills, and workforce capabilities.</t>
         </is>
       </c>
+      <c r="D46" s="5" t="n"/>
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="5" t="n"/>
+      <c r="G46" s="5" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>Army</t>
         </is>
       </c>
-      <c r="B47" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>IND-000046</t>
         </is>
       </c>
-      <c r="C47" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>Protects national security through military operations, defense planning, and peacekeeping activities. Employs personnel in combat, engineering, intelligence, logistics, healthcare, and administration. Focuses on readiness, discipline, and national defense.</t>
         </is>
       </c>
+      <c r="D47" s="5" t="n"/>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="5" t="n"/>
+      <c r="G47" s="5" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>Government</t>
         </is>
       </c>
-      <c r="B48" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>IND-000047</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>Delivers public administration, policy development, regulation, and public services. Includes local, regional, and national government agencies. Supports economic development, public safety, healthcare, education, and infrastructure.</t>
         </is>
       </c>
+      <c r="D48" s="5" t="n"/>
+      <c r="E48" s="5" t="n"/>
+      <c r="F48" s="5" t="n"/>
+      <c r="G48" s="5" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1" password="DB2D"/>

--- a/apps/api/data/excel_templates/industries.xlsx
+++ b/apps/api/data/excel_templates/industries.xlsx
@@ -56,7 +56,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
       <protection locked="0" hidden="0"/>
@@ -66,9 +66,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <protection locked="0" hidden="0"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -484,991 +481,803 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>Agriculture and Forestry</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>IND-000001</t>
         </is>
       </c>
-      <c r="C2" s="5" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Produces crops, livestock, timber, and other natural resources. Includes farming, forestry management, and agricultural technology. Supports global food supply, raw materials, and environmental sustainability.</t>
         </is>
       </c>
-      <c r="D2" s="5" t="n"/>
-      <c r="E2" s="5" t="n"/>
-      <c r="F2" s="5" t="n"/>
-      <c r="G2" s="5" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>Mining</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>IND-000002</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Extracts minerals, metals, coal, and other natural resources from the earth. Uses exploration, drilling, and processing technologies. Supplies essential materials for manufacturing, energy, and construction.</t>
         </is>
       </c>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>Pulp and Paper Industry</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>IND-000003</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Manufactures paper, cardboard, packaging, and pulp products from wood and recycled fibers. Focuses on sustainable production and recycling. Serves publishing, packaging, and consumer goods markets.</t>
         </is>
       </c>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
-      <c r="G4" s="5" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>Automotive</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>IND-000004</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Designs, manufactures, and sells cars, trucks, motorcycles, and vehicle components. Covers electric vehicles, autonomous driving, and mobility technologies. Employs engineers, technicians, and manufacturing specialists.</t>
         </is>
       </c>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" t="inlineStr">
         <is>
           <t>Chemical Industry</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" t="inlineStr">
         <is>
           <t>IND-000005</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Produces industrial chemicals, plastics, fertilizers, coatings, and specialty materials. Supports numerous sectors including agriculture, healthcare, and manufacturing. Emphasizes innovation, safety, and environmental compliance.</t>
         </is>
       </c>
-      <c r="D6" s="5" t="n"/>
-      <c r="E6" s="5" t="n"/>
-      <c r="F6" s="5" t="n"/>
-      <c r="G6" s="5" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Construction</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" t="inlineStr">
         <is>
           <t>IND-000006</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Plans, builds, and maintains residential, commercial, and infrastructure projects. Includes architecture, engineering, project management, and skilled trades. Drives urban development and economic growth.</t>
         </is>
       </c>
-      <c r="D7" s="5" t="n"/>
-      <c r="E7" s="5" t="n"/>
-      <c r="F7" s="5" t="n"/>
-      <c r="G7" s="5" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" t="inlineStr">
         <is>
           <t>Durable Consumer Goods</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>IND-000007</t>
         </is>
       </c>
-      <c r="C8" s="5" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Manufactures long-lasting consumer products such as appliances, furniture, and household equipment. Focuses on product quality, innovation, and customer satisfaction. Products are typically used for several years.</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n"/>
-      <c r="E8" s="5" t="n"/>
-      <c r="F8" s="5" t="n"/>
-      <c r="G8" s="5" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" t="inlineStr">
         <is>
           <t>Electronics</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" t="inlineStr">
         <is>
           <t>IND-000008</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Develops and manufactures electronic devices, components, and systems. Includes consumer electronics, industrial equipment, and embedded technologies. Innovation and rapid product development are key drivers.</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n"/>
-      <c r="E9" s="5" t="n"/>
-      <c r="F9" s="5" t="n"/>
-      <c r="G9" s="5" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>IND-000009</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Produces and distributes electricity, oil, natural gas, and renewable energy. Invests in power generation, energy storage, and sustainability initiatives. Plays a critical role in economic development.</t>
         </is>
       </c>
-      <c r="D10" s="5" t="n"/>
-      <c r="E10" s="5" t="n"/>
-      <c r="F10" s="5" t="n"/>
-      <c r="G10" s="5" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" t="inlineStr">
         <is>
           <t>Fast-Moving Consumer Goods (FMCG)</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>IND-000010</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Produces and markets everyday products such as food, beverages, toiletries, and household items. Operates with high sales volumes and rapid inventory turnover. Success depends on branding, distribution, and supply chains.</t>
         </is>
       </c>
-      <c r="D11" s="5" t="n"/>
-      <c r="E11" s="5" t="n"/>
-      <c r="F11" s="5" t="n"/>
-      <c r="G11" s="5" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>Food Industry</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>IND-000011</t>
         </is>
       </c>
-      <c r="C12" s="5" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Processes, manufactures, packages, and distributes food and beverages. Ensures product quality, food safety, and regulatory compliance. Serves consumers, retailers, and food service businesses worldwide.</t>
         </is>
       </c>
-      <c r="D12" s="5" t="n"/>
-      <c r="E12" s="5" t="n"/>
-      <c r="F12" s="5" t="n"/>
-      <c r="G12" s="5" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" t="inlineStr">
         <is>
           <t>Heavy Manufacturing</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>IND-000012</t>
         </is>
       </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="C13" t="inlineStr">
         <is>
           <t>Produces large-scale industrial equipment, machinery, ships, and heavy infrastructure components. Requires advanced engineering and significant capital investment. Supports construction, transportation, and energy sectors.</t>
         </is>
       </c>
-      <c r="D13" s="5" t="n"/>
-      <c r="E13" s="5" t="n"/>
-      <c r="F13" s="5" t="n"/>
-      <c r="G13" s="5" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" t="inlineStr">
         <is>
           <t>Industrial Goods</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>IND-000013</t>
         </is>
       </c>
-      <c r="C14" s="5" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Manufactures machinery, tools, industrial equipment, and production materials for businesses. Focuses on efficiency, reliability, and automation. Supplies manufacturing, construction, and infrastructure industries.</t>
         </is>
       </c>
-      <c r="D14" s="5" t="n"/>
-      <c r="E14" s="5" t="n"/>
-      <c r="F14" s="5" t="n"/>
-      <c r="G14" s="5" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" t="inlineStr">
         <is>
           <t>Medical Devices</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>IND-000014</t>
         </is>
       </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="C15" t="inlineStr">
         <is>
           <t>Designs and manufactures equipment used for diagnosis, monitoring, and treatment. Products range from surgical instruments to advanced imaging systems. Strict quality standards and regulatory compliance are essential.</t>
         </is>
       </c>
-      <c r="D15" s="5" t="n"/>
-      <c r="E15" s="5" t="n"/>
-      <c r="F15" s="5" t="n"/>
-      <c r="G15" s="5" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>Office and Communication Equipment</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>IND-000015</t>
         </is>
       </c>
-      <c r="C16" s="5" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Produces office machines, printers, networking equipment, and communication hardware. Supports workplace productivity and business communications. Continuously evolves with advances in digital technology.</t>
         </is>
       </c>
-      <c r="D16" s="5" t="n"/>
-      <c r="E16" s="5" t="n"/>
-      <c r="F16" s="5" t="n"/>
-      <c r="G16" s="5" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" t="inlineStr">
         <is>
           <t>Pharmaceutical</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>IND-000016</t>
         </is>
       </c>
-      <c r="C17" s="5" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Discovers, develops, manufactures, and markets medicines and vaccines. Invests heavily in research, clinical trials, and regulatory approval. Improves healthcare outcomes through innovative therapies.</t>
         </is>
       </c>
-      <c r="D17" s="5" t="n"/>
-      <c r="E17" s="5" t="n"/>
-      <c r="F17" s="5" t="n"/>
-      <c r="G17" s="5" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Utilities</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>IND-000017</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Provides essential public services including electricity, water, gas, and wastewater management. Operates critical infrastructure with high reliability requirements. Often functions under government regulation.</t>
         </is>
       </c>
-      <c r="D18" s="5" t="n"/>
-      <c r="E18" s="5" t="n"/>
-      <c r="F18" s="5" t="n"/>
-      <c r="G18" s="5" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Advertising &amp; Marketing</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>IND-000018</t>
         </is>
       </c>
-      <c r="C19" s="5" t="inlineStr">
+      <c r="C19" t="inlineStr">
         <is>
           <t>Creates campaigns that promote brands, products, and services. Uses market research, creative content, digital platforms, and analytics. Helps organizations attract and retain customers.</t>
         </is>
       </c>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-      <c r="G19" s="5" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" t="inlineStr">
         <is>
           <t>Banking</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>IND-000019</t>
         </is>
       </c>
-      <c r="C20" s="5" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Provides financial services including deposits, loans, payments, and wealth management. Supports individuals, businesses, and governments. Operates under strict financial regulations and risk management standards.</t>
         </is>
       </c>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-      <c r="G20" s="5" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" t="inlineStr">
         <is>
           <t>Business Services</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>IND-000020</t>
         </is>
       </c>
-      <c r="C21" s="5" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>Delivers professional support such as outsourcing, administration, customer service, and facility management. Helps organizations improve efficiency and reduce costs. Serves businesses across multiple industries.</t>
         </is>
       </c>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-      <c r="G21" s="5" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" t="inlineStr">
         <is>
           <t>Entertainment and Broadcasting</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>IND-000021</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Produces and distributes television, radio, film, music, and digital media content. Combines creativity with media technology and distribution platforms. Generates revenue through advertising, subscriptions, and licensing.</t>
         </is>
       </c>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
-      <c r="G22" s="5" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" t="inlineStr">
         <is>
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>IND-000022</t>
         </is>
       </c>
-      <c r="C23" s="5" t="inlineStr">
+      <c r="C23" t="inlineStr">
         <is>
           <t>Offers investment, asset management, brokerage, lending, and financial advisory services. Helps individuals and organizations manage capital and financial risks. Relies on regulatory compliance and financial expertise.</t>
         </is>
       </c>
-      <c r="D23" s="5" t="n"/>
-      <c r="E23" s="5" t="n"/>
-      <c r="F23" s="5" t="n"/>
-      <c r="G23" s="5" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" t="inlineStr">
         <is>
           <t>Hospitality</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>IND-000023</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C24" t="inlineStr">
         <is>
           <t>Provides accommodation, food service, tourism, and event management. Focuses on customer experience and service quality. Includes hotels, restaurants, resorts, and travel businesses.</t>
         </is>
       </c>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-      <c r="G24" s="5" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>IND-000024</t>
         </is>
       </c>
-      <c r="C25" s="5" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Protects individuals and organizations against financial losses through insurance products. Covers life, health, property, and commercial risks. Relies on underwriting, actuarial analysis, and claims management.</t>
         </is>
       </c>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-      <c r="G25" s="5" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="A26" t="inlineStr">
         <is>
           <t>Legal Services</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>IND-000025</t>
         </is>
       </c>
-      <c r="C26" s="5" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Provides legal advice, representation, compliance, and dispute resolution. Serves businesses, governments, and individuals. Requires expertise in laws, regulations, and legal procedures.</t>
         </is>
       </c>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="A27" t="inlineStr">
         <is>
           <t>Management Consulting</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>IND-000026</t>
         </is>
       </c>
-      <c r="C27" s="5" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>Advises organizations on strategy, operations, technology, and organizational improvement. Helps clients solve business challenges and improve performance. Consultants work across many industries and functions.</t>
         </is>
       </c>
-      <c r="D27" s="5" t="n"/>
-      <c r="E27" s="5" t="n"/>
-      <c r="F27" s="5" t="n"/>
-      <c r="G27" s="5" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="A28" t="inlineStr">
         <is>
           <t>Personal Services</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>IND-000027</t>
         </is>
       </c>
-      <c r="C28" s="5" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>Delivers services directly to consumers, including beauty, wellness, fitness, and personal care. Focuses on customer relationships and service quality. Demand is driven by lifestyle and consumer preferences.</t>
         </is>
       </c>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-      <c r="G28" s="5" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="5" t="inlineStr">
+      <c r="A29" t="inlineStr">
         <is>
           <t>Publishing</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>IND-000028</t>
         </is>
       </c>
-      <c r="C29" s="5" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Produces books, journals, newspapers, magazines, and digital publications. Manages editorial, production, and content distribution processes. Increasingly emphasizes digital platforms and online content.</t>
         </is>
       </c>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
-      <c r="G29" s="5" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="5" t="inlineStr">
+      <c r="A30" t="inlineStr">
         <is>
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>IND-000029</t>
         </is>
       </c>
-      <c r="C30" s="5" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>Develops, buys, sells, leases, and manages residential and commercial properties. Includes property investment, construction, and facility management. Supports housing, business, and infrastructure needs.</t>
         </is>
       </c>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="n"/>
-      <c r="G30" s="5" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="5" t="inlineStr">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Recruitment</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>IND-000030</t>
         </is>
       </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="C31" t="inlineStr">
         <is>
           <t>Helps organizations attract, assess, and hire employees. Provides staffing, executive search, and workforce solutions. Supports employers across industries and job levels.</t>
         </is>
       </c>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
-      <c r="G31" s="5" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="5" t="inlineStr">
+      <c r="A32" t="inlineStr">
         <is>
           <t>Retail</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>IND-000031</t>
         </is>
       </c>
-      <c r="C32" s="5" t="inlineStr">
+      <c r="C32" t="inlineStr">
         <is>
           <t>Sells products directly to consumers through physical stores and online platforms. Manages merchandising, customer service, and inventory. Success depends on consumer demand and efficient supply chains.</t>
         </is>
       </c>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
-      <c r="G32" s="5" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="5" t="inlineStr">
+      <c r="A33" t="inlineStr">
         <is>
           <t>Transport</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>IND-000032</t>
         </is>
       </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>Moves people and goods by road, rail, air, and sea. Includes logistics, freight, shipping, and public transportation. Plays a vital role in global trade and economic activity.</t>
         </is>
       </c>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-      <c r="G33" s="5" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="5" t="inlineStr">
+      <c r="A34" t="inlineStr">
         <is>
           <t>Computer Hardware</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>IND-000033</t>
         </is>
       </c>
-      <c r="C34" s="5" t="inlineStr">
+      <c r="C34" t="inlineStr">
         <is>
           <t>Designs and manufactures computers, servers, storage devices, and related hardware. Focuses on performance, reliability, and innovation. Supports consumer, enterprise, and industrial computing.</t>
         </is>
       </c>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="n"/>
-      <c r="G34" s="5" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="5" t="inlineStr">
+      <c r="A35" t="inlineStr">
         <is>
           <t>Computer Software</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>IND-000034</t>
         </is>
       </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="C35" t="inlineStr">
         <is>
           <t>Develops software applications and operating systems for personal and business use. Covers design, coding, testing, and maintenance. Drives digital transformation across industries.</t>
         </is>
       </c>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="n"/>
-      <c r="G35" s="5" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="5" t="inlineStr">
+      <c r="A36" t="inlineStr">
         <is>
           <t>Enterprise Software</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>IND-000035</t>
         </is>
       </c>
-      <c r="C36" s="5" t="inlineStr">
+      <c r="C36" t="inlineStr">
         <is>
           <t>Creates software solutions for business operations such as ERP, CRM, finance, and HR systems. Helps organizations improve efficiency and decision-making. Typically serves medium and large enterprises.</t>
         </is>
       </c>
-      <c r="D36" s="5" t="n"/>
-      <c r="E36" s="5" t="n"/>
-      <c r="F36" s="5" t="n"/>
-      <c r="G36" s="5" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="5" t="inlineStr">
+      <c r="A37" t="inlineStr">
         <is>
           <t>Gaming Industry</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>IND-000036</t>
         </is>
       </c>
-      <c r="C37" s="5" t="inlineStr">
+      <c r="C37" t="inlineStr">
         <is>
           <t>Develops, publishes, and distributes video games across consoles, PCs, and mobile devices. Combines software development, storytelling, design, and online services. Revenue comes from game sales, subscriptions, and in-game purchases.</t>
         </is>
       </c>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="5" t="n"/>
-      <c r="F37" s="5" t="n"/>
-      <c r="G37" s="5" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Industry Specific Software</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>IND-000037</t>
         </is>
       </c>
-      <c r="C38" s="5" t="inlineStr">
+      <c r="C38" t="inlineStr">
         <is>
           <t>Develops software tailored to specialized industries such as healthcare, finance, manufacturing, or education. Addresses unique regulatory and operational requirements. Enables organizations to improve productivity and compliance.</t>
         </is>
       </c>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5" t="n"/>
-      <c r="G38" s="5" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
+      <c r="A39" t="inlineStr">
         <is>
           <t>IT Services</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>IND-000038</t>
         </is>
       </c>
-      <c r="C39" s="5" t="inlineStr">
+      <c r="C39" t="inlineStr">
         <is>
           <t>Provides technology consulting, systems integration, cloud services, cybersecurity, and technical support. Helps organizations implement and manage IT infrastructure. Enables digital transformation and operational efficiency.</t>
         </is>
       </c>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5" t="n"/>
-      <c r="G39" s="5" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="5" t="inlineStr">
+      <c r="A40" t="inlineStr">
         <is>
           <t>Mobile Applications</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>IND-000039</t>
         </is>
       </c>
-      <c r="C40" s="5" t="inlineStr">
+      <c r="C40" t="inlineStr">
         <is>
           <t>Designs and develops software for smartphones, tablets, and mobile devices. Covers consumer apps, enterprise solutions, and mobile commerce. Focuses on usability, performance, and continuous updates.</t>
         </is>
       </c>
-      <c r="D40" s="5" t="n"/>
-      <c r="E40" s="5" t="n"/>
-      <c r="F40" s="5" t="n"/>
-      <c r="G40" s="5" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+      <c r="A41" t="inlineStr">
         <is>
           <t>Online Services</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>IND-000040</t>
         </is>
       </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="C41" t="inlineStr">
         <is>
           <t>Delivers internet-based services such as e-commerce, cloud platforms, streaming, social media, and digital marketplaces. Operates through web and mobile technologies. Business models often rely on subscriptions, advertising, or transactions.</t>
         </is>
       </c>
-      <c r="D41" s="5" t="n"/>
-      <c r="E41" s="5" t="n"/>
-      <c r="F41" s="5" t="n"/>
-      <c r="G41" s="5" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="5" t="inlineStr">
+      <c r="A42" t="inlineStr">
         <is>
           <t>PC Consumer Software</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>IND-000041</t>
         </is>
       </c>
-      <c r="C42" s="5" t="inlineStr">
+      <c r="C42" t="inlineStr">
         <is>
           <t>Develops desktop software for productivity, creativity, security, and entertainment. Serves individual users and small businesses. Emphasizes usability, compatibility, and regular feature updates.</t>
         </is>
       </c>
-      <c r="D42" s="5" t="n"/>
-      <c r="E42" s="5" t="n"/>
-      <c r="F42" s="5" t="n"/>
-      <c r="G42" s="5" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="5" t="inlineStr">
+      <c r="A43" t="inlineStr">
         <is>
           <t>Robotics</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B43" t="inlineStr">
         <is>
           <t>IND-000042</t>
         </is>
       </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="C43" t="inlineStr">
         <is>
           <t>Designs and builds robotic systems for manufacturing, healthcare, logistics, and service applications. Combines mechanical engineering, electronics, and artificial intelligence. Improves automation, productivity, and precision.</t>
         </is>
       </c>
-      <c r="D43" s="5" t="n"/>
-      <c r="E43" s="5" t="n"/>
-      <c r="F43" s="5" t="n"/>
-      <c r="G43" s="5" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="5" t="inlineStr">
+      <c r="A44" t="inlineStr">
         <is>
           <t>Semiconductor</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B44" t="inlineStr">
         <is>
           <t>IND-000043</t>
         </is>
       </c>
-      <c r="C44" s="5" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Designs and manufactures integrated circuits, microprocessors, memory chips, and electronic components. Forms the foundation of modern computing and communications. Requires advanced fabrication technologies and significant research investment.</t>
         </is>
       </c>
-      <c r="D44" s="5" t="n"/>
-      <c r="E44" s="5" t="n"/>
-      <c r="F44" s="5" t="n"/>
-      <c r="G44" s="5" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="5" t="inlineStr">
+      <c r="A45" t="inlineStr">
         <is>
           <t>Telecommunications</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B45" t="inlineStr">
         <is>
           <t>IND-000044</t>
         </is>
       </c>
-      <c r="C45" s="5" t="inlineStr">
+      <c r="C45" t="inlineStr">
         <is>
           <t>Provides voice, data, internet, and wireless communication services. Builds and operates communication networks and infrastructure. Supports businesses, governments, and consumers worldwide.</t>
         </is>
       </c>
-      <c r="D45" s="5" t="n"/>
-      <c r="E45" s="5" t="n"/>
-      <c r="F45" s="5" t="n"/>
-      <c r="G45" s="5" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+      <c r="A46" t="inlineStr">
         <is>
           <t>Education</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B46" t="inlineStr">
         <is>
           <t>IND-000045</t>
         </is>
       </c>
-      <c r="C46" s="5" t="inlineStr">
+      <c r="C46" t="inlineStr">
         <is>
           <t>Provides teaching, learning, training, and academic research services. Includes schools, universities, vocational institutions, and educational technology providers. Develops knowledge, skills, and workforce capabilities.</t>
         </is>
       </c>
-      <c r="D46" s="5" t="n"/>
-      <c r="E46" s="5" t="n"/>
-      <c r="F46" s="5" t="n"/>
-      <c r="G46" s="5" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
+      <c r="A47" t="inlineStr">
         <is>
           <t>Army</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B47" t="inlineStr">
         <is>
           <t>IND-000046</t>
         </is>
       </c>
-      <c r="C47" s="5" t="inlineStr">
+      <c r="C47" t="inlineStr">
         <is>
           <t>Protects national security through military operations, defense planning, and peacekeeping activities. Employs personnel in combat, engineering, intelligence, logistics, healthcare, and administration. Focuses on readiness, discipline, and national defense.</t>
         </is>
       </c>
-      <c r="D47" s="5" t="n"/>
-      <c r="E47" s="5" t="n"/>
-      <c r="F47" s="5" t="n"/>
-      <c r="G47" s="5" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+      <c r="A48" t="inlineStr">
         <is>
           <t>Government</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B48" t="inlineStr">
         <is>
           <t>IND-000047</t>
         </is>
       </c>
-      <c r="C48" s="5" t="inlineStr">
+      <c r="C48" t="inlineStr">
         <is>
           <t>Delivers public administration, policy development, regulation, and public services. Includes local, regional, and national government agencies. Supports economic development, public safety, healthcare, education, and infrastructure.</t>
         </is>
       </c>
-      <c r="D48" s="5" t="n"/>
-      <c r="E48" s="5" t="n"/>
-      <c r="F48" s="5" t="n"/>
-      <c r="G48" s="5" t="n"/>
     </row>
   </sheetData>
   <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1" password="DB2D"/>
